--- a/Execução Financeira 2026.xlsx
+++ b/Execução Financeira 2026.xlsx
@@ -850,10 +850,10 @@
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="10">
-        <v>8331076.63</v>
+        <v>13923393.39</v>
       </c>
       <c r="J18" s="11">
-        <v>8331076.63</v>
+        <v>13923393.39</v>
       </c>
     </row>
     <row r="19">
@@ -3400,10 +3400,10 @@
       </c>
       <c r="H103" s="10"/>
       <c r="I103" s="10">
-        <v>541.15</v>
+        <v>10396123.54</v>
       </c>
       <c r="J103" s="11">
-        <v>541.15</v>
+        <v>10396123.54</v>
       </c>
     </row>
     <row r="104">
@@ -4000,10 +4000,10 @@
       </c>
       <c r="H123" s="10"/>
       <c r="I123" s="10">
-        <v>0</v>
+        <v>1247346</v>
       </c>
       <c r="J123" s="11">
-        <v>0</v>
+        <v>1247346</v>
       </c>
     </row>
     <row r="124">
@@ -4510,10 +4510,10 @@
       </c>
       <c r="H140" s="10"/>
       <c r="I140" s="10">
-        <v>301825.28</v>
+        <v>1631968.29</v>
       </c>
       <c r="J140" s="11">
-        <v>301825.28</v>
+        <v>1631968.29</v>
       </c>
     </row>
     <row r="141">
@@ -4794,10 +4794,10 @@
         <v>0</v>
       </c>
       <c r="I149" s="10">
-        <v>72577.51</v>
+        <v>1748887.56</v>
       </c>
       <c r="J149" s="11">
-        <v>72577.51</v>
+        <v>1748887.56</v>
       </c>
     </row>
     <row r="150">
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="I171" s="10">
-        <v>0</v>
+        <v>1527751</v>
       </c>
       <c r="J171" s="11">
-        <v>0</v>
+        <v>1527751</v>
       </c>
     </row>
     <row r="172">
@@ -6084,10 +6084,10 @@
       </c>
       <c r="H191" s="10"/>
       <c r="I191" s="10">
-        <v>0</v>
+        <v>154669.32</v>
       </c>
       <c r="J191" s="11">
-        <v>0</v>
+        <v>154669.32</v>
       </c>
     </row>
     <row r="192">
@@ -6397,13 +6397,13 @@
         <v>29</v>
       </c>
       <c r="H201" s="10">
-        <v>1009069.32</v>
+        <v>2741622.15</v>
       </c>
       <c r="I201" s="10">
-        <v>607169.48</v>
+        <v>662791.84</v>
       </c>
       <c r="J201" s="11">
-        <v>1616238.8</v>
+        <v>3404413.99</v>
       </c>
     </row>
     <row r="202">
@@ -7120,10 +7120,10 @@
       </c>
       <c r="H225" s="10"/>
       <c r="I225" s="10">
-        <v>0</v>
+        <v>955009.7</v>
       </c>
       <c r="J225" s="11">
-        <v>0</v>
+        <v>955009.7</v>
       </c>
     </row>
     <row r="226">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="H235" s="10"/>
       <c r="I235" s="10">
-        <v>8664.99</v>
+        <v>5407468</v>
       </c>
       <c r="J235" s="11">
-        <v>8664.99</v>
+        <v>5407468</v>
       </c>
     </row>
     <row r="236">
@@ -9310,10 +9310,10 @@
       </c>
       <c r="H298" s="10"/>
       <c r="I298" s="10">
-        <v>72.13</v>
+        <v>726861.46</v>
       </c>
       <c r="J298" s="11">
-        <v>72.13</v>
+        <v>726861.46</v>
       </c>
     </row>
     <row r="299">
@@ -10390,10 +10390,10 @@
       </c>
       <c r="H334" s="10"/>
       <c r="I334" s="10">
-        <v>0</v>
+        <v>3014367.6</v>
       </c>
       <c r="J334" s="11">
-        <v>0</v>
+        <v>3014367.6</v>
       </c>
     </row>
     <row r="335">
@@ -10690,10 +10690,10 @@
       </c>
       <c r="H344" s="10"/>
       <c r="I344" s="10">
-        <v>4950868.73</v>
+        <v>6362883.39</v>
       </c>
       <c r="J344" s="11">
-        <v>4950868.73</v>
+        <v>6362883.39</v>
       </c>
     </row>
     <row r="345">
@@ -13040,10 +13040,10 @@
       </c>
       <c r="H422" s="10"/>
       <c r="I422" s="10">
-        <v>164176.01</v>
+        <v>2742040.51</v>
       </c>
       <c r="J422" s="11">
-        <v>164176.01</v>
+        <v>2742040.51</v>
       </c>
     </row>
     <row r="423">
@@ -13940,10 +13940,10 @@
       </c>
       <c r="H452" s="10"/>
       <c r="I452" s="10">
-        <v>162388.27</v>
+        <v>3261986.94</v>
       </c>
       <c r="J452" s="11">
-        <v>162388.27</v>
+        <v>3261986.94</v>
       </c>
     </row>
     <row r="453">
@@ -13957,13 +13957,13 @@
       <c r="F453" s="12"/>
       <c r="G453" s="12" t="s"/>
       <c r="H453" s="13">
-        <v>479919555.9</v>
+        <v>481652108.73</v>
       </c>
       <c r="I453" s="13">
-        <v>2723663297.82</v>
+        <v>2762827486.18</v>
       </c>
       <c r="J453" s="11">
-        <v>3203582853.72</v>
+        <v>3244479594.91</v>
       </c>
     </row>
   </sheetData>
@@ -14235,13 +14235,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2070142-BB8A-493E-815E-F38DF74742A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1704F5F-D95C-46EF-AE12-0A9DA6D21C5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE29690D-0AD5-4012-A333-9512218D4C16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA39F3-78E9-40AC-917B-CC742F83EA9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D30849-8614-4F20-BA9F-037F89707D42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4CEEF25-C0BE-4E65-AEAA-DEC246D0694A}"/>
 </file>
--- a/Execução Financeira 2026.xlsx
+++ b/Execução Financeira 2026.xlsx
@@ -850,10 +850,10 @@
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="10">
-        <v>13923393.39</v>
+        <v>59821375.33</v>
       </c>
       <c r="J18" s="11">
-        <v>13923393.39</v>
+        <v>59821375.33</v>
       </c>
     </row>
     <row r="19">
@@ -1450,10 +1450,10 @@
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="10">
-        <v>1761.76</v>
+        <v>41980.1</v>
       </c>
       <c r="J38" s="11">
-        <v>1761.76</v>
+        <v>41980.1</v>
       </c>
     </row>
     <row r="39">
@@ -1750,10 +1750,10 @@
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="10">
-        <v>15678024.48</v>
+        <v>17116662.83</v>
       </c>
       <c r="J48" s="11">
-        <v>15678024.48</v>
+        <v>17116662.83</v>
       </c>
     </row>
     <row r="49">
@@ -2050,10 +2050,10 @@
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="10">
-        <v>0</v>
+        <v>1065356</v>
       </c>
       <c r="J58" s="11">
-        <v>0</v>
+        <v>1065356</v>
       </c>
     </row>
     <row r="59">
@@ -2620,10 +2620,10 @@
       </c>
       <c r="H77" s="10"/>
       <c r="I77" s="10">
-        <v>0</v>
+        <v>55810.1</v>
       </c>
       <c r="J77" s="11">
-        <v>0</v>
+        <v>55810.1</v>
       </c>
     </row>
     <row r="78">
@@ -3400,10 +3400,10 @@
       </c>
       <c r="H103" s="10"/>
       <c r="I103" s="10">
-        <v>10396123.54</v>
+        <v>11459829.08</v>
       </c>
       <c r="J103" s="11">
-        <v>10396123.54</v>
+        <v>11459829.08</v>
       </c>
     </row>
     <row r="104">
@@ -3700,10 +3700,10 @@
       </c>
       <c r="H113" s="10"/>
       <c r="I113" s="10">
-        <v>287306</v>
+        <v>337792</v>
       </c>
       <c r="J113" s="11">
-        <v>287306</v>
+        <v>337792</v>
       </c>
     </row>
     <row r="114">
@@ -4000,10 +4000,10 @@
       </c>
       <c r="H123" s="10"/>
       <c r="I123" s="10">
-        <v>1247346</v>
+        <v>1402006.37</v>
       </c>
       <c r="J123" s="11">
-        <v>1247346</v>
+        <v>1402006.37</v>
       </c>
     </row>
     <row r="124">
@@ -4270,10 +4270,10 @@
       </c>
       <c r="H132" s="10"/>
       <c r="I132" s="10">
-        <v>16598045.01</v>
+        <v>17991407.67</v>
       </c>
       <c r="J132" s="11">
-        <v>16598045.01</v>
+        <v>17991407.67</v>
       </c>
     </row>
     <row r="133">
@@ -4794,10 +4794,10 @@
         <v>0</v>
       </c>
       <c r="I149" s="10">
-        <v>1748887.56</v>
+        <v>2696834.86</v>
       </c>
       <c r="J149" s="11">
-        <v>1748887.56</v>
+        <v>2696834.86</v>
       </c>
     </row>
     <row r="150">
@@ -5226,10 +5226,10 @@
         <v>35256.67</v>
       </c>
       <c r="I163" s="10">
-        <v>1934677</v>
+        <v>2002726.29</v>
       </c>
       <c r="J163" s="11">
-        <v>1969933.67</v>
+        <v>2037982.96</v>
       </c>
     </row>
     <row r="164">
@@ -5784,10 +5784,10 @@
         <v>47189.7</v>
       </c>
       <c r="I181" s="10">
-        <v>590095.66</v>
+        <v>2158687.1</v>
       </c>
       <c r="J181" s="11">
-        <v>637285.36</v>
+        <v>2205876.8</v>
       </c>
     </row>
     <row r="182">
@@ -6397,13 +6397,13 @@
         <v>29</v>
       </c>
       <c r="H201" s="10">
-        <v>2741622.15</v>
+        <v>15665649.14</v>
       </c>
       <c r="I201" s="10">
-        <v>662791.84</v>
+        <v>1048486.05</v>
       </c>
       <c r="J201" s="11">
-        <v>3404413.99</v>
+        <v>16714135.19</v>
       </c>
     </row>
     <row r="202">
@@ -6820,10 +6820,10 @@
       </c>
       <c r="H215" s="10"/>
       <c r="I215" s="10">
-        <v>0</v>
+        <v>451630.23</v>
       </c>
       <c r="J215" s="11">
-        <v>0</v>
+        <v>451630.23</v>
       </c>
     </row>
     <row r="216">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="H235" s="10"/>
       <c r="I235" s="10">
-        <v>5407468</v>
+        <v>6401816.68</v>
       </c>
       <c r="J235" s="11">
-        <v>5407468</v>
+        <v>6401816.68</v>
       </c>
     </row>
     <row r="236">
@@ -9310,10 +9310,10 @@
       </c>
       <c r="H298" s="10"/>
       <c r="I298" s="10">
-        <v>726861.46</v>
+        <v>734358.34</v>
       </c>
       <c r="J298" s="11">
-        <v>726861.46</v>
+        <v>734358.34</v>
       </c>
     </row>
     <row r="299">
@@ -10390,10 +10390,10 @@
       </c>
       <c r="H334" s="10"/>
       <c r="I334" s="10">
-        <v>3014367.6</v>
+        <v>3176463.49</v>
       </c>
       <c r="J334" s="11">
-        <v>3014367.6</v>
+        <v>3176463.49</v>
       </c>
     </row>
     <row r="335">
@@ -10690,10 +10690,10 @@
       </c>
       <c r="H344" s="10"/>
       <c r="I344" s="10">
-        <v>6362883.39</v>
+        <v>6615283.48</v>
       </c>
       <c r="J344" s="11">
-        <v>6362883.39</v>
+        <v>6615283.48</v>
       </c>
     </row>
     <row r="345">
@@ -13040,10 +13040,10 @@
       </c>
       <c r="H422" s="10"/>
       <c r="I422" s="10">
-        <v>2742040.51</v>
+        <v>5654165.99</v>
       </c>
       <c r="J422" s="11">
-        <v>2742040.51</v>
+        <v>5654165.99</v>
       </c>
     </row>
     <row r="423">
@@ -13340,10 +13340,10 @@
       </c>
       <c r="H432" s="10"/>
       <c r="I432" s="10">
-        <v>588136.04</v>
+        <v>613524.04</v>
       </c>
       <c r="J432" s="11">
-        <v>588136.04</v>
+        <v>613524.04</v>
       </c>
     </row>
     <row r="433">
@@ -13640,10 +13640,10 @@
       </c>
       <c r="H442" s="10"/>
       <c r="I442" s="10">
-        <v>75962.7</v>
+        <v>1837360.69</v>
       </c>
       <c r="J442" s="11">
-        <v>75962.7</v>
+        <v>1837360.69</v>
       </c>
     </row>
     <row r="443">
@@ -13940,10 +13940,10 @@
       </c>
       <c r="H452" s="10"/>
       <c r="I452" s="10">
-        <v>3261986.94</v>
+        <v>7478350.26</v>
       </c>
       <c r="J452" s="11">
-        <v>3261986.94</v>
+        <v>7478350.26</v>
       </c>
     </row>
     <row r="453">
@@ -13957,13 +13957,13 @@
       <c r="F453" s="12"/>
       <c r="G453" s="12" t="s"/>
       <c r="H453" s="13">
-        <v>481652108.73</v>
+        <v>494576135.72</v>
       </c>
       <c r="I453" s="13">
-        <v>2762827486.18</v>
+        <v>2827741234.28</v>
       </c>
       <c r="J453" s="11">
-        <v>3244479594.91</v>
+        <v>3322317370</v>
       </c>
     </row>
   </sheetData>
@@ -14235,13 +14235,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1704F5F-D95C-46EF-AE12-0A9DA6D21C5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9140F111-6CC2-4C49-B092-64CD3CBDBE71}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9EA39F3-78E9-40AC-917B-CC742F83EA9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196AB629-0D1A-4E68-B1C3-91421980C10A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4CEEF25-C0BE-4E65-AEAA-DEC246D0694A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{964012E3-FD71-45B3-917C-DA7763743E78}"/>
 </file>